--- a/TrainingLOG.xlsx
+++ b/TrainingLOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main_IMN\MSF_IMN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D9569C-9655-4C97-A3B3-362DEF53ABBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF9DA25-AAF1-4FC8-8208-86D15649696A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A717A7A0-4C05-44F3-807A-4EB99306429C}"/>
   </bookViews>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F53312-B091-4286-B72A-CEF546F62BA0}">
-  <dimension ref="A2:H6"/>
+  <dimension ref="A2:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="20.7109375" customWidth="1"/>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -534,6 +534,11 @@
       </c>
       <c r="H6">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>904</v>
       </c>
     </row>
   </sheetData>
